--- a/artfynd/A 10000-2022 artfynd.xlsx
+++ b/artfynd/A 10000-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10000-2022 artfynd.xlsx
+++ b/artfynd/A 10000-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101249079</v>
+        <v>117989504</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100770</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fuessly, 1775)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +708,40 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fraktvägen,Sigtuna, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664498.5476361637</v>
+        <v>664411</v>
       </c>
       <c r="R2" t="n">
-        <v>6613938.556150104</v>
+        <v>6614011</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +765,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,33 +779,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Födosökande på getväppling</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Livbom</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Livbom, Theodor Sjöblom</t>
+          <t>Björn Bråvander, Carina Lerdahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101249056</v>
+        <v>120751924</v>
       </c>
       <c r="B3" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,26 +814,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102964</v>
+        <v>102124</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Vinterhämpling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Linaria flavirostris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -847,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664498.5476361637</v>
+        <v>664498</v>
       </c>
       <c r="R3" t="n">
-        <v>6613938.556150104</v>
+        <v>6613939</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,22 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +911,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Livbom, Theodor Sjöblom</t>
+          <t>Andreas Livbom</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -922,16 +921,11 @@
         <v>101249055</v>
       </c>
       <c r="B4" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -967,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664498.5476361637</v>
+        <v>664498</v>
       </c>
       <c r="R4" t="n">
-        <v>6613938.556150104</v>
+        <v>6613939</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1039,15 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101249071</v>
+        <v>101249063</v>
       </c>
       <c r="B5" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,35 +1044,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664498.5476361637</v>
+        <v>664498</v>
       </c>
       <c r="R5" t="n">
-        <v>6613938.556150104</v>
+        <v>6613939</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1166,12 +1151,7 @@
         <v>101249064</v>
       </c>
       <c r="B6" t="n">
-        <v>56608</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664498.5476361637</v>
+        <v>664498</v>
       </c>
       <c r="R6" t="n">
-        <v>6613938.556150104</v>
+        <v>6613939</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1283,32 +1263,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120751924</v>
+        <v>101249071</v>
       </c>
       <c r="B7" t="n">
-        <v>57996</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102124</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1318,12 +1293,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1361,22 +1340,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1375,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Livbom</t>
+          <t>Andreas Livbom, Theodor Sjöblom</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1406,12 +1385,7 @@
         <v>120751925</v>
       </c>
       <c r="B8" t="n">
-        <v>58024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,6 +1495,832 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>101249079</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fraktvägen,Sigtuna, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>664498</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6613939</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Livbom</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Livbom, Theodor Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130077334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>664828</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6614159</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130077335</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>664707</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6613922</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130077338</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>664685</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6613904</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130077339</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>664833</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6614222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130077344</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>664815</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6614118</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130077346</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>664821</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6614130</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130077349</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>664697</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6613914</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10000-2022 artfynd.xlsx
+++ b/artfynd/A 10000-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,53 +1033,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101249063</v>
+        <v>134763137</v>
       </c>
       <c r="B5" t="n">
-        <v>58209</v>
+        <v>57796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fraktvägen,Sigtuna, Upl</t>
+          <t>Prästgårdsskogen, Prästgårdsskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664498</v>
+        <v>664700</v>
       </c>
       <c r="R5" t="n">
-        <v>6613939</v>
+        <v>6614136</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,22 +1098,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,49 +1118,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Livbom</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Livbom, Theodor Sjöblom</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101249064</v>
+        <v>101249063</v>
       </c>
       <c r="B6" t="n">
-        <v>58212</v>
+        <v>58209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1263,27 +1245,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101249071</v>
+        <v>101249064</v>
       </c>
       <c r="B7" t="n">
-        <v>58286</v>
+        <v>58212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>102981</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1293,16 +1275,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1382,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120751925</v>
+        <v>101249071</v>
       </c>
       <c r="B8" t="n">
-        <v>58636</v>
+        <v>58286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,16 +1371,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1412,12 +1390,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1455,22 +1437,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,53 +1472,49 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Livbom</t>
+          <t>Andreas Livbom, Theodor Sjöblom</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101249079</v>
+        <v>120751925</v>
       </c>
       <c r="B9" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1574,22 +1552,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,17 +1587,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Livbom, Theodor Sjöblom</t>
+          <t>Andreas Livbom</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130077334</v>
+        <v>101249079</v>
       </c>
       <c r="B10" t="n">
-        <v>102559</v>
+        <v>58676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,37 +1605,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222133</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Cargo, Arlanda, Upl</t>
+          <t>Fraktvägen,Sigtuna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664828</v>
+        <v>664498</v>
       </c>
       <c r="R10" t="n">
-        <v>6614159</v>
+        <v>6613939</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,12 +1671,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,64 +1701,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Andreas Livbom</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Andreas Livbom, Theodor Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130077335</v>
+        <v>134761102</v>
       </c>
       <c r="B11" t="n">
-        <v>102559</v>
+        <v>107943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222133</v>
+        <v>219933</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Cargo, Arlanda, Upl</t>
+          <t>Prästgårdsskogen, Prästgårdsskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664707</v>
+        <v>664895</v>
       </c>
       <c r="R11" t="n">
-        <v>6613922</v>
+        <v>6614439</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,23 +1798,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130077338</v>
+        <v>130077334</v>
       </c>
       <c r="B12" t="n">
         <v>102559</v>
@@ -1853,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>664685</v>
+        <v>664828</v>
       </c>
       <c r="R12" t="n">
-        <v>6613904</v>
+        <v>6614159</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1919,7 +1911,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130077339</v>
+        <v>130077335</v>
       </c>
       <c r="B13" t="n">
         <v>102559</v>
@@ -1954,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>664833</v>
+        <v>664707</v>
       </c>
       <c r="R13" t="n">
-        <v>6614222</v>
+        <v>6613922</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2020,7 +2012,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130077344</v>
+        <v>130077338</v>
       </c>
       <c r="B14" t="n">
         <v>102559</v>
@@ -2055,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>664815</v>
+        <v>664685</v>
       </c>
       <c r="R14" t="n">
-        <v>6614118</v>
+        <v>6613904</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2121,7 +2113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130077346</v>
+        <v>130077339</v>
       </c>
       <c r="B15" t="n">
         <v>102559</v>
@@ -2156,10 +2148,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>664821</v>
+        <v>664833</v>
       </c>
       <c r="R15" t="n">
-        <v>6614130</v>
+        <v>6614222</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2222,7 +2214,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130077349</v>
+        <v>130077344</v>
       </c>
       <c r="B16" t="n">
         <v>102559</v>
@@ -2257,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664697</v>
+        <v>664815</v>
       </c>
       <c r="R16" t="n">
-        <v>6613914</v>
+        <v>6614118</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2316,6 +2308,208 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130077346</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>664821</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6614130</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130077349</v>
+      </c>
+      <c r="B18" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Cargo, Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>664697</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6613914</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby-Ärlinghundra</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 10000-2022 artfynd.xlsx
+++ b/artfynd/A 10000-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117989504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120751924</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101249055</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763137</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101249063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101249064</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101249071</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1591,6 +1631,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120751925</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101249079</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761102</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077334</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077335</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2110,6 +2175,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077338</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2211,6 +2281,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077339</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077344</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2413,6 +2493,11 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077346</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,8 +2599,32 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077349</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>